--- a/Datas/PastureDataList.xlsx
+++ b/Datas/PastureDataList.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="23">
   <si>
     <t>pastureName</t>
   </si>
@@ -27,9 +27,6 @@
     <t>id</t>
   </si>
   <si>
-    <t>linkItem</t>
-  </si>
-  <si>
     <t>string</t>
   </si>
   <si>
@@ -74,15 +71,31 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1003,2|1004,2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>successTalk</t>
+  </si>
+  <si>
+    <t>int2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>animationKey</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1001,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -422,45 +435,45 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" t="s">
         <v>6</v>
-      </c>
-      <c r="B1" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="D2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
@@ -471,42 +484,42 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="D3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" t="s">
         <v>9</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>10</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" t="s">
         <v>11</v>
       </c>
-      <c r="G3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J3" t="s">
         <v>12</v>
       </c>
-      <c r="I3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>13</v>
-      </c>
-      <c r="K3" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B4">
         <v>3000</v>
       </c>
-      <c r="C4">
-        <v>1093</v>
+      <c r="C4" t="s">
+        <v>20</v>
       </c>
       <c r="D4">
         <v>12</v>
@@ -527,7 +540,7 @@
         <v>100</v>
       </c>
       <c r="J4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K4">
         <v>2</v>
@@ -535,13 +548,13 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5">
         <v>3000</v>
       </c>
-      <c r="C5">
-        <v>1058</v>
+      <c r="C5" t="s">
+        <v>21</v>
       </c>
       <c r="D5">
         <v>12</v>
@@ -562,7 +575,7 @@
         <v>200</v>
       </c>
       <c r="J5" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="K5">
         <v>4</v>

--- a/Datas/PastureDataList.xlsx
+++ b/Datas/PastureDataList.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="21">
   <si>
     <t>pastureName</t>
   </si>
@@ -67,10 +67,6 @@
     <t>List&lt;int2&gt;</t>
   </si>
   <si>
-    <t>1001,2|1002,2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -91,10 +87,6 @@
   </si>
   <si>
     <t>2,0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1001,2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -449,7 +441,7 @@
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D2" t="s">
         <v>3</v>
@@ -461,7 +453,7 @@
         <v>3</v>
       </c>
       <c r="G2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H2" t="s">
         <v>3</v>
@@ -484,7 +476,7 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
@@ -496,7 +488,7 @@
         <v>10</v>
       </c>
       <c r="G3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H3" t="s">
         <v>11</v>
@@ -519,7 +511,7 @@
         <v>3000</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D4">
         <v>12</v>
@@ -537,10 +529,7 @@
         <v>1</v>
       </c>
       <c r="I4">
-        <v>100</v>
-      </c>
-      <c r="J4" t="s">
-        <v>15</v>
+        <v>5600</v>
       </c>
       <c r="K4">
         <v>2</v>
@@ -554,7 +543,7 @@
         <v>3000</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D5">
         <v>12</v>
@@ -572,10 +561,7 @@
         <v>2</v>
       </c>
       <c r="I5">
-        <v>200</v>
-      </c>
-      <c r="J5" t="s">
-        <v>22</v>
+        <v>15000</v>
       </c>
       <c r="K5">
         <v>4</v>

--- a/Datas/PastureDataList.xlsx
+++ b/Datas/PastureDataList.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="23">
   <si>
     <t>pastureName</t>
   </si>
@@ -87,6 +87,14 @@
   </si>
   <si>
     <t>2,0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>105,50|201,50</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>105,100|201,100</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -422,7 +430,7 @@
     <col min="6" max="7" width="14.25" customWidth="1"/>
     <col min="8" max="8" width="7.375" customWidth="1"/>
     <col min="9" max="9" width="11.375" customWidth="1"/>
-    <col min="10" max="10" width="10.5" customWidth="1"/>
+    <col min="10" max="10" width="42.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
@@ -529,7 +537,10 @@
         <v>1</v>
       </c>
       <c r="I4">
-        <v>5600</v>
+        <v>3200</v>
+      </c>
+      <c r="J4" t="s">
+        <v>21</v>
       </c>
       <c r="K4">
         <v>2</v>
@@ -561,7 +572,10 @@
         <v>2</v>
       </c>
       <c r="I5">
-        <v>15000</v>
+        <v>9800</v>
+      </c>
+      <c r="J5" t="s">
+        <v>22</v>
       </c>
       <c r="K5">
         <v>4</v>
